--- a/data/nzd0511/nzd0511.xlsx
+++ b/data/nzd0511/nzd0511.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L485"/>
+  <dimension ref="A1:L490"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20778,6 +20778,216 @@
         <v>310.65</v>
       </c>
       <c r="L485" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:13:56+00:00</t>
+        </is>
+      </c>
+      <c r="B486" t="n">
+        <v>284.12</v>
+      </c>
+      <c r="C486" t="n">
+        <v>287.23</v>
+      </c>
+      <c r="D486" t="n">
+        <v>287.96</v>
+      </c>
+      <c r="E486" t="n">
+        <v>294.76</v>
+      </c>
+      <c r="F486" t="n">
+        <v>309.78</v>
+      </c>
+      <c r="G486" t="n">
+        <v>336.72</v>
+      </c>
+      <c r="H486" t="n">
+        <v>381.6</v>
+      </c>
+      <c r="I486" t="n">
+        <v>379.45</v>
+      </c>
+      <c r="J486" t="n">
+        <v>342.29</v>
+      </c>
+      <c r="K486" t="n">
+        <v>302.1</v>
+      </c>
+      <c r="L486" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B487" t="n">
+        <v>282.89</v>
+      </c>
+      <c r="C487" t="n">
+        <v>286.06</v>
+      </c>
+      <c r="D487" t="n">
+        <v>288.35</v>
+      </c>
+      <c r="E487" t="n">
+        <v>294.25</v>
+      </c>
+      <c r="F487" t="n">
+        <v>307.69</v>
+      </c>
+      <c r="G487" t="n">
+        <v>333.25</v>
+      </c>
+      <c r="H487" t="n">
+        <v>378.57</v>
+      </c>
+      <c r="I487" t="n">
+        <v>377.32</v>
+      </c>
+      <c r="J487" t="n">
+        <v>339.51</v>
+      </c>
+      <c r="K487" t="n">
+        <v>290.27</v>
+      </c>
+      <c r="L487" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:15+00:00</t>
+        </is>
+      </c>
+      <c r="B488" t="n">
+        <v>282.6</v>
+      </c>
+      <c r="C488" t="n">
+        <v>285.99</v>
+      </c>
+      <c r="D488" t="n">
+        <v>288.3</v>
+      </c>
+      <c r="E488" t="n">
+        <v>293.56</v>
+      </c>
+      <c r="F488" t="n">
+        <v>306.37</v>
+      </c>
+      <c r="G488" t="n">
+        <v>330.48</v>
+      </c>
+      <c r="H488" t="n">
+        <v>372.72</v>
+      </c>
+      <c r="I488" t="n">
+        <v>377.32</v>
+      </c>
+      <c r="J488" t="n">
+        <v>339.51</v>
+      </c>
+      <c r="K488" t="n">
+        <v>283.55</v>
+      </c>
+      <c r="L488" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:14:16+00:00</t>
+        </is>
+      </c>
+      <c r="B489" t="n">
+        <v>280.49</v>
+      </c>
+      <c r="C489" t="n">
+        <v>284.52</v>
+      </c>
+      <c r="D489" t="n">
+        <v>287.23</v>
+      </c>
+      <c r="E489" t="n">
+        <v>292.58</v>
+      </c>
+      <c r="F489" t="n">
+        <v>304.86</v>
+      </c>
+      <c r="G489" t="n">
+        <v>327.67</v>
+      </c>
+      <c r="H489" t="n">
+        <v>366.45</v>
+      </c>
+      <c r="I489" t="n">
+        <v>377.32</v>
+      </c>
+      <c r="J489" t="n">
+        <v>339.51</v>
+      </c>
+      <c r="K489" t="n">
+        <v>278.39</v>
+      </c>
+      <c r="L489" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:32+00:00</t>
+        </is>
+      </c>
+      <c r="B490" t="n">
+        <v>280.49</v>
+      </c>
+      <c r="C490" t="n">
+        <v>284.72</v>
+      </c>
+      <c r="D490" t="n">
+        <v>287.58</v>
+      </c>
+      <c r="E490" t="n">
+        <v>292.7</v>
+      </c>
+      <c r="F490" t="n">
+        <v>304.61</v>
+      </c>
+      <c r="G490" t="n">
+        <v>326.85</v>
+      </c>
+      <c r="H490" t="n">
+        <v>366.45</v>
+      </c>
+      <c r="I490" t="n">
+        <v>374.89</v>
+      </c>
+      <c r="J490" t="n">
+        <v>339.22</v>
+      </c>
+      <c r="K490" t="n">
+        <v>278.39</v>
+      </c>
+      <c r="L490" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -20794,7 +21004,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B554"/>
+  <dimension ref="A1:B559"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26337,6 +26547,56 @@
       </c>
       <c r="B554" t="n">
         <v>-0.78</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B555" t="n">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B556" t="n">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B557" t="n">
+        <v>-0.23</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B558" t="n">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B559" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -26505,28 +26765,28 @@
         <v>0.0578</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3036401488072882</v>
+        <v>-0.301897950674491</v>
       </c>
       <c r="J2" t="n">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="K2" t="n">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06033434661290504</v>
+        <v>0.06082154855927713</v>
       </c>
       <c r="M2" t="n">
-        <v>7.410899721341495</v>
+        <v>7.350748764382381</v>
       </c>
       <c r="N2" t="n">
-        <v>82.081038711841</v>
+        <v>81.26569389504695</v>
       </c>
       <c r="O2" t="n">
-        <v>9.059858647453668</v>
+        <v>9.014748687292784</v>
       </c>
       <c r="P2" t="n">
-        <v>289.3571984529688</v>
+        <v>289.3383550271072</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26583,28 +26843,28 @@
         <v>0.0464</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3576981096748998</v>
+        <v>-0.3426670007249948</v>
       </c>
       <c r="J3" t="n">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="K3" t="n">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06655737732908884</v>
+        <v>0.06223651975356126</v>
       </c>
       <c r="M3" t="n">
-        <v>8.388484536717733</v>
+        <v>8.382660860267009</v>
       </c>
       <c r="N3" t="n">
-        <v>102.574741446983</v>
+        <v>102.1618750532891</v>
       </c>
       <c r="O3" t="n">
-        <v>10.12791890997272</v>
+        <v>10.10751577061788</v>
       </c>
       <c r="P3" t="n">
-        <v>287.3591611992277</v>
+        <v>287.1963106187575</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26661,28 +26921,28 @@
         <v>0.0497</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4733013025128675</v>
+        <v>-0.4578272809339437</v>
       </c>
       <c r="J4" t="n">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="K4" t="n">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09744544214651663</v>
+        <v>0.09299089999577226</v>
       </c>
       <c r="M4" t="n">
-        <v>8.636667164998167</v>
+        <v>8.632957934480391</v>
       </c>
       <c r="N4" t="n">
-        <v>118.5998141624944</v>
+        <v>118.0553588423396</v>
       </c>
       <c r="O4" t="n">
-        <v>10.89035417984624</v>
+        <v>10.86532828967168</v>
       </c>
       <c r="P4" t="n">
-        <v>292.4015231643113</v>
+        <v>292.2340919403878</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26739,28 +26999,28 @@
         <v>0.0428</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4407332102863902</v>
+        <v>-0.4323385307436308</v>
       </c>
       <c r="J5" t="n">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="K5" t="n">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09352433731121601</v>
+        <v>0.09185129322218422</v>
       </c>
       <c r="M5" t="n">
-        <v>8.134796603720002</v>
+        <v>8.096290347028903</v>
       </c>
       <c r="N5" t="n">
-        <v>107.6174980776656</v>
+        <v>106.7211939545202</v>
       </c>
       <c r="O5" t="n">
-        <v>10.37388538965346</v>
+        <v>10.3305950435839</v>
       </c>
       <c r="P5" t="n">
-        <v>300.9618897713752</v>
+        <v>300.8711434619153</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26817,28 +27077,28 @@
         <v>0.0483</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2486556099503847</v>
+        <v>-0.2499557198350184</v>
       </c>
       <c r="J6" t="n">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="K6" t="n">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02542706920501836</v>
+        <v>0.02619644339554583</v>
       </c>
       <c r="M6" t="n">
-        <v>9.187972120706455</v>
+        <v>9.112263455697926</v>
       </c>
       <c r="N6" t="n">
-        <v>135.4610356708373</v>
+        <v>134.1177563831431</v>
       </c>
       <c r="O6" t="n">
-        <v>11.63877294523943</v>
+        <v>11.58092208691273</v>
       </c>
       <c r="P6" t="n">
-        <v>314.0322074634703</v>
+        <v>314.0463156969249</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26895,28 +27155,28 @@
         <v>0.0315</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1262650793884448</v>
+        <v>0.1146458188565899</v>
       </c>
       <c r="J7" t="n">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="K7" t="n">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00339712188072927</v>
+        <v>0.002854738869260465</v>
       </c>
       <c r="M7" t="n">
-        <v>12.77417915514972</v>
+        <v>12.69978455714279</v>
       </c>
       <c r="N7" t="n">
-        <v>265.4206878591232</v>
+        <v>263.2045376483806</v>
       </c>
       <c r="O7" t="n">
-        <v>16.2917367968895</v>
+        <v>16.2235796804645</v>
       </c>
       <c r="P7" t="n">
-        <v>333.7161805406046</v>
+        <v>333.8426614381822</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26973,28 +27233,28 @@
         <v>0.0261</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3317575539945779</v>
+        <v>0.3551665958249017</v>
       </c>
       <c r="J8" t="n">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="K8" t="n">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01573336437288608</v>
+        <v>0.01826834217698037</v>
       </c>
       <c r="M8" t="n">
-        <v>16.26038650950531</v>
+        <v>16.21734328926642</v>
       </c>
       <c r="N8" t="n">
-        <v>389.2249905883487</v>
+        <v>387.1264921775535</v>
       </c>
       <c r="O8" t="n">
-        <v>19.72878583664866</v>
+        <v>19.6755302896149</v>
       </c>
       <c r="P8" t="n">
-        <v>351.9285164904487</v>
+        <v>351.6732564694269</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27051,28 +27311,28 @@
         <v>0.0209</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5013325564793724</v>
+        <v>0.5296383499988279</v>
       </c>
       <c r="J9" t="n">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="K9" t="n">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0297899284307499</v>
+        <v>0.03363809611702673</v>
       </c>
       <c r="M9" t="n">
-        <v>17.54344080995666</v>
+        <v>17.51763456573097</v>
       </c>
       <c r="N9" t="n">
-        <v>466.9292205394942</v>
+        <v>464.3896379404293</v>
       </c>
       <c r="O9" t="n">
-        <v>21.60854508150639</v>
+        <v>21.54970157427776</v>
       </c>
       <c r="P9" t="n">
-        <v>348.8087427933439</v>
+        <v>348.5019370935587</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27129,28 +27389,28 @@
         <v>0.0283</v>
       </c>
       <c r="I10" t="n">
-        <v>0.645241476970046</v>
+        <v>0.6630173107912425</v>
       </c>
       <c r="J10" t="n">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="K10" t="n">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0359220213624093</v>
+        <v>0.03855561786238015</v>
       </c>
       <c r="M10" t="n">
-        <v>19.94888454910701</v>
+        <v>19.82171151406689</v>
       </c>
       <c r="N10" t="n">
-        <v>633.9914368622988</v>
+        <v>628.3826608426883</v>
       </c>
       <c r="O10" t="n">
-        <v>25.1791865806324</v>
+        <v>25.0675619245807</v>
       </c>
       <c r="P10" t="n">
-        <v>313.2856672748011</v>
+        <v>313.0924992380102</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -27207,28 +27467,28 @@
         <v>0.0801</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4898953295366738</v>
+        <v>0.4655322300661329</v>
       </c>
       <c r="J11" t="n">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="K11" t="n">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01396770016528426</v>
+        <v>0.012855423915342</v>
       </c>
       <c r="M11" t="n">
-        <v>25.02279026508137</v>
+        <v>24.91846403865912</v>
       </c>
       <c r="N11" t="n">
-        <v>966.0515685978055</v>
+        <v>958.5606785380901</v>
       </c>
       <c r="O11" t="n">
-        <v>31.08137012098735</v>
+        <v>30.96063110690882</v>
       </c>
       <c r="P11" t="n">
-        <v>286.2007890765478</v>
+        <v>286.4654519022369</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -27270,7 +27530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L485"/>
+  <dimension ref="A1:L490"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57267,6 +57527,316 @@
         </is>
       </c>
     </row>
+    <row r="486">
+      <c r="A486" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:13:56+00:00</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>-45.90696285894467,170.5636016623495</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>-45.907115221863904,170.56272863634248</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>-45.907246520184756,170.56185010727106</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>-45.90743154130092,170.56098561120226</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>-45.9076874797632,170.5601537478192</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>-45.90800579057505,170.5593170645414</t>
+        </is>
+      </c>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>-45.90844023873645,170.55843781160786</t>
+        </is>
+      </c>
+      <c r="I486" t="inlineStr">
+        <is>
+          <t>-45.9084521073672,170.5575317118313</t>
+        </is>
+      </c>
+      <c r="J486" t="inlineStr">
+        <is>
+          <t>-45.908127917116325,170.55662461883682</t>
+        </is>
+      </c>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>-45.90762119754101,170.55589002316967</t>
+        </is>
+      </c>
+      <c r="L486" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>-45.9069519727566,170.56359881839956</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>-45.907104866698695,170.56272593122688</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>-45.9072499719101,170.56185100894078</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>-45.907427027501654,170.56098443214037</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>-45.90766887041063,170.56014989467644</t>
+        </is>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>-45.907974644361786,170.55931403478982</t>
+        </is>
+      </c>
+      <c r="H487" t="inlineStr">
+        <is>
+          <t>-45.908412990805836,170.5584366759833</t>
+        </is>
+      </c>
+      <c r="I487" t="inlineStr">
+        <is>
+          <t>-45.90843294654245,170.55753133980417</t>
+        </is>
+      </c>
+      <c r="J487" t="inlineStr">
+        <is>
+          <t>-45.908103146126166,170.55662956331918</t>
+        </is>
+      </c>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>-45.90751874672556,170.55593131530867</t>
+        </is>
+      </c>
+      <c r="L487" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:15+00:00</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>-45.90694940609435,170.5635981478749</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>-45.9071042471589,170.5627257693824</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>-45.9072495293812,170.5618508933421</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>-45.907420920596756,170.56098283693933</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>-45.907657117135265,170.56014746111381</t>
+        </is>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>-45.907949781246174,170.55931161622925</t>
+        </is>
+      </c>
+      <c r="H488" t="inlineStr">
+        <is>
+          <t>-45.90836038341471,170.55843448344245</t>
+        </is>
+      </c>
+      <c r="I488" t="inlineStr">
+        <is>
+          <t>-45.90843294654245,170.55753133980417</t>
+        </is>
+      </c>
+      <c r="J488" t="inlineStr">
+        <is>
+          <t>-45.908103146126166,170.55662956331918</t>
+        </is>
+      </c>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>-45.907460549803886,170.55595477112735</t>
+        </is>
+      </c>
+      <c r="L488" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:14:16+00:00</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>-45.90693073141382,170.56359326923186</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>-45.90709123682303,170.56272237064883</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>-45.90724005926295,170.56184841953055</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>-45.90741224702165,170.560980571292</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>-45.9076436721005,170.56014467726678</t>
+        </is>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>-45.90792455909632,170.55930916274536</t>
+        </is>
+      </c>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>-45.90830399908226,170.55843213349073</t>
+        </is>
+      </c>
+      <c r="I489" t="inlineStr">
+        <is>
+          <t>-45.90843294654245,170.55753133980417</t>
+        </is>
+      </c>
+      <c r="J489" t="inlineStr">
+        <is>
+          <t>-45.908103146126166,170.55662956331918</t>
+        </is>
+      </c>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>-45.907415862877556,170.5559727818104</t>
+        </is>
+      </c>
+      <c r="L489" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:32+00:00</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>-45.90693073141382,170.56359326923186</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>-45.907093006936755,170.56272283306146</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>-45.907243156965194,170.56184922872117</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>-45.90741330909207,170.56098084871817</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>-45.907641446101344,170.56014421636507</t>
+        </is>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>-45.90791719889597,170.55930844678244</t>
+        </is>
+      </c>
+      <c r="H490" t="inlineStr">
+        <is>
+          <t>-45.90830399908226,170.55843213349073</t>
+        </is>
+      </c>
+      <c r="I490" t="inlineStr">
+        <is>
+          <t>-45.908411087009924,170.5575309153788</t>
+        </is>
+      </c>
+      <c r="J490" t="inlineStr">
+        <is>
+          <t>-45.908100562101986,170.55663007911022</t>
+        </is>
+      </c>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>-45.907415862877556,170.5559727818104</t>
+        </is>
+      </c>
+      <c r="L490" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0511/nzd0511.xlsx
+++ b/data/nzd0511/nzd0511.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L490"/>
+  <dimension ref="A1:L491"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20958,7 +20958,7 @@
         </is>
       </c>
       <c r="B490" t="n">
-        <v>280.49</v>
+        <v>281.1</v>
       </c>
       <c r="C490" t="n">
         <v>284.72</v>
@@ -20976,7 +20976,7 @@
         <v>326.85</v>
       </c>
       <c r="H490" t="n">
-        <v>366.45</v>
+        <v>364.67</v>
       </c>
       <c r="I490" t="n">
         <v>374.89</v>
@@ -20985,11 +20985,53 @@
         <v>339.22</v>
       </c>
       <c r="K490" t="n">
-        <v>278.39</v>
+        <v>279.68</v>
       </c>
       <c r="L490" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:20:25+00:00</t>
+        </is>
+      </c>
+      <c r="B491" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="C491" t="n">
+        <v>283.62</v>
+      </c>
+      <c r="D491" t="n">
+        <v>286.69</v>
+      </c>
+      <c r="E491" t="n">
+        <v>291.61</v>
+      </c>
+      <c r="F491" t="n">
+        <v>303.24</v>
+      </c>
+      <c r="G491" t="n">
+        <v>324.9</v>
+      </c>
+      <c r="H491" t="n">
+        <v>362.21</v>
+      </c>
+      <c r="I491" t="n">
+        <v>370.34</v>
+      </c>
+      <c r="J491" t="n">
+        <v>336.67</v>
+      </c>
+      <c r="K491" t="n">
+        <v>279.81</v>
+      </c>
+      <c r="L491" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -21004,7 +21046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B559"/>
+  <dimension ref="A1:B560"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26597,6 +26639,16 @@
       </c>
       <c r="B559" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B560" t="n">
+        <v>-0.18</v>
       </c>
     </row>
   </sheetData>
@@ -26765,28 +26817,28 @@
         <v>0.0578</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.301897950674491</v>
+        <v>-0.3021299133041573</v>
       </c>
       <c r="J2" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="K2" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06082154855927713</v>
+        <v>0.06113874945344111</v>
       </c>
       <c r="M2" t="n">
-        <v>7.350748764382381</v>
+        <v>7.336792827227614</v>
       </c>
       <c r="N2" t="n">
-        <v>81.26569389504695</v>
+        <v>81.10081483023315</v>
       </c>
       <c r="O2" t="n">
-        <v>9.014748687292784</v>
+        <v>9.005599082250617</v>
       </c>
       <c r="P2" t="n">
-        <v>289.3383550271072</v>
+        <v>289.3408776431842</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26843,28 +26895,28 @@
         <v>0.0464</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3426670007249948</v>
+        <v>-0.3405319906344295</v>
       </c>
       <c r="J3" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="K3" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06223651975356126</v>
+        <v>0.06170678168044763</v>
       </c>
       <c r="M3" t="n">
-        <v>8.382660860267009</v>
+        <v>8.376859685626584</v>
       </c>
       <c r="N3" t="n">
-        <v>102.1618750532891</v>
+        <v>102.0174390650501</v>
       </c>
       <c r="O3" t="n">
-        <v>10.10751577061788</v>
+        <v>10.10036826383326</v>
       </c>
       <c r="P3" t="n">
-        <v>287.1963106187575</v>
+        <v>287.173115550239</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26921,28 +26973,28 @@
         <v>0.0497</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4578272809339437</v>
+        <v>-0.4552676560184569</v>
       </c>
       <c r="J4" t="n">
+        <v>490</v>
+      </c>
+      <c r="K4" t="n">
         <v>489</v>
       </c>
-      <c r="K4" t="n">
-        <v>488</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.09299089999577226</v>
+        <v>0.09232056337465622</v>
       </c>
       <c r="M4" t="n">
-        <v>8.632957934480391</v>
+        <v>8.629231514296947</v>
       </c>
       <c r="N4" t="n">
-        <v>118.0553588423396</v>
+        <v>117.9076952767123</v>
       </c>
       <c r="O4" t="n">
-        <v>10.86532828967168</v>
+        <v>10.85853099073315</v>
       </c>
       <c r="P4" t="n">
-        <v>292.2340919403878</v>
+        <v>292.2063237907455</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26999,28 +27051,28 @@
         <v>0.0428</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4323385307436308</v>
+        <v>-0.4314400307485972</v>
       </c>
       <c r="J5" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="K5" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09185129322218422</v>
+        <v>0.09183204585757088</v>
       </c>
       <c r="M5" t="n">
-        <v>8.096290347028903</v>
+        <v>8.084572444482099</v>
       </c>
       <c r="N5" t="n">
-        <v>106.7211939545202</v>
+        <v>106.5149393387849</v>
       </c>
       <c r="O5" t="n">
-        <v>10.3305950435839</v>
+        <v>10.32060750822281</v>
       </c>
       <c r="P5" t="n">
-        <v>300.8711434619153</v>
+        <v>300.8614032814824</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27077,28 +27129,28 @@
         <v>0.0483</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2499557198350184</v>
+        <v>-0.2514903986984769</v>
       </c>
       <c r="J6" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="K6" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02619644339554583</v>
+        <v>0.02660846347195001</v>
       </c>
       <c r="M6" t="n">
-        <v>9.112263455697926</v>
+        <v>9.101862445152857</v>
       </c>
       <c r="N6" t="n">
-        <v>134.1177563831431</v>
+        <v>133.8777246050617</v>
       </c>
       <c r="O6" t="n">
-        <v>11.58092208691273</v>
+        <v>11.57055420475016</v>
       </c>
       <c r="P6" t="n">
-        <v>314.0463156969249</v>
+        <v>314.0629523681762</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27155,28 +27207,28 @@
         <v>0.0315</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1146458188565899</v>
+        <v>0.1100835875231863</v>
       </c>
       <c r="J7" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="K7" t="n">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002854738869260465</v>
+        <v>0.002640327180930546</v>
       </c>
       <c r="M7" t="n">
-        <v>12.69978455714279</v>
+        <v>12.69607786282752</v>
       </c>
       <c r="N7" t="n">
-        <v>263.2045376483806</v>
+        <v>262.9601716270441</v>
       </c>
       <c r="O7" t="n">
-        <v>16.2235796804645</v>
+        <v>16.21604673238962</v>
       </c>
       <c r="P7" t="n">
-        <v>333.8426614381822</v>
+        <v>333.8924132159217</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27233,28 +27285,28 @@
         <v>0.0261</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3551665958249017</v>
+        <v>0.3548569714634843</v>
       </c>
       <c r="J8" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="K8" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01826834217698037</v>
+        <v>0.01831110583083417</v>
       </c>
       <c r="M8" t="n">
-        <v>16.21734328926642</v>
+        <v>16.18239001331588</v>
       </c>
       <c r="N8" t="n">
-        <v>387.1264921775535</v>
+        <v>386.3018116469268</v>
       </c>
       <c r="O8" t="n">
-        <v>19.6755302896149</v>
+        <v>19.65456210773791</v>
       </c>
       <c r="P8" t="n">
-        <v>351.6732564694269</v>
+        <v>351.6766359317771</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27311,28 +27363,28 @@
         <v>0.0209</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5296383499988279</v>
+        <v>0.5324970595567549</v>
       </c>
       <c r="J9" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="K9" t="n">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03363809611702673</v>
+        <v>0.03411436990336159</v>
       </c>
       <c r="M9" t="n">
-        <v>17.51763456573097</v>
+        <v>17.49721434841428</v>
       </c>
       <c r="N9" t="n">
-        <v>464.3896379404293</v>
+        <v>463.5546368652685</v>
       </c>
       <c r="O9" t="n">
-        <v>21.54970157427776</v>
+        <v>21.53031901447975</v>
       </c>
       <c r="P9" t="n">
-        <v>348.5019370935587</v>
+        <v>348.4708673683675</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27389,28 +27441,28 @@
         <v>0.0283</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6630173107912425</v>
+        <v>0.6651854098434886</v>
       </c>
       <c r="J10" t="n">
+        <v>490</v>
+      </c>
+      <c r="K10" t="n">
         <v>489</v>
       </c>
-      <c r="K10" t="n">
-        <v>488</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.03855561786238015</v>
+        <v>0.03894578246191915</v>
       </c>
       <c r="M10" t="n">
-        <v>19.82171151406689</v>
+        <v>19.79052351062181</v>
       </c>
       <c r="N10" t="n">
-        <v>628.3826608426883</v>
+        <v>627.1641373167862</v>
       </c>
       <c r="O10" t="n">
-        <v>25.0675619245807</v>
+        <v>25.04324534314166</v>
       </c>
       <c r="P10" t="n">
-        <v>313.0924992380102</v>
+        <v>313.0688743588055</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -27467,28 +27519,28 @@
         <v>0.0801</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4655322300661329</v>
+        <v>0.4587516269971845</v>
       </c>
       <c r="J11" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="K11" t="n">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="L11" t="n">
-        <v>0.012855423915342</v>
+        <v>0.01252985115935468</v>
       </c>
       <c r="M11" t="n">
-        <v>24.91846403865912</v>
+        <v>24.90656330096177</v>
       </c>
       <c r="N11" t="n">
-        <v>958.5606785380901</v>
+        <v>957.2360856620827</v>
       </c>
       <c r="O11" t="n">
-        <v>30.96063110690882</v>
+        <v>30.93923214402844</v>
       </c>
       <c r="P11" t="n">
-        <v>286.4654519022369</v>
+        <v>286.5392405280729</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -27530,7 +27582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L490"/>
+  <dimension ref="A1:L491"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57783,7 +57835,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>-45.90693073141382,170.56359326923186</t>
+          <t>-45.90693613025513,170.56359467964492</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
@@ -57813,7 +57865,7 @@
       </c>
       <c r="H490" t="inlineStr">
         <is>
-          <t>-45.90830399908226,170.55843213349073</t>
+          <t>-45.90828799204681,170.55843146635976</t>
         </is>
       </c>
       <c r="I490" t="inlineStr">
@@ -57828,12 +57880,74 @@
       </c>
       <c r="K490" t="inlineStr">
         <is>
-          <t>-45.907415862877556,170.5559727818104</t>
+          <t>-45.907427034609505,170.55596827914246</t>
         </is>
       </c>
       <c r="L490" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:20:25+00:00</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>-45.90692630613405,170.56359211315572</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>-45.907083271311215,170.56272028979222</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>-45.90723527995093,170.56184717106524</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>-45.90740366195235,170.56097832876418</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>-45.90762924762603,170.5601416906243</t>
+        </is>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>-45.9078996959805,170.55930674418823</t>
+        </is>
+      </c>
+      <c r="H491" t="inlineStr">
+        <is>
+          <t>-45.90826586996403,170.55843054437005</t>
+        </is>
+      </c>
+      <c r="I491" t="inlineStr">
+        <is>
+          <t>-45.90837015660932,170.55753012067282</t>
+        </is>
+      </c>
+      <c r="J491" t="inlineStr">
+        <is>
+          <t>-45.908077840509904,170.55663461451198</t>
+        </is>
+      </c>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>-45.90742816044294,170.55596782538512</t>
+        </is>
+      </c>
+      <c r="L491" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>

--- a/data/nzd0511/nzd0511.xlsx
+++ b/data/nzd0511/nzd0511.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L491"/>
+  <dimension ref="A1:L494"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21032,6 +21032,132 @@
       <c r="L491" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:14:25+00:00</t>
+        </is>
+      </c>
+      <c r="B492" t="n">
+        <v>279.13</v>
+      </c>
+      <c r="C492" t="n">
+        <v>283.24</v>
+      </c>
+      <c r="D492" t="n">
+        <v>285.47</v>
+      </c>
+      <c r="E492" t="n">
+        <v>289.38</v>
+      </c>
+      <c r="F492" t="n">
+        <v>300.52</v>
+      </c>
+      <c r="G492" t="n">
+        <v>320.32</v>
+      </c>
+      <c r="H492" t="n">
+        <v>359.83</v>
+      </c>
+      <c r="I492" t="n">
+        <v>368.25</v>
+      </c>
+      <c r="J492" t="n">
+        <v>337.23</v>
+      </c>
+      <c r="K492" t="n">
+        <v>275.76</v>
+      </c>
+      <c r="L492" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:37+00:00</t>
+        </is>
+      </c>
+      <c r="B493" t="n">
+        <v>278.8</v>
+      </c>
+      <c r="C493" t="n">
+        <v>282.47</v>
+      </c>
+      <c r="D493" t="n">
+        <v>284.84</v>
+      </c>
+      <c r="E493" t="n">
+        <v>288.65</v>
+      </c>
+      <c r="F493" t="n">
+        <v>299.4</v>
+      </c>
+      <c r="G493" t="n">
+        <v>319.12</v>
+      </c>
+      <c r="H493" t="n">
+        <v>358.15</v>
+      </c>
+      <c r="I493" t="n">
+        <v>366.83</v>
+      </c>
+      <c r="J493" t="n">
+        <v>336.97</v>
+      </c>
+      <c r="K493" t="n">
+        <v>277.12</v>
+      </c>
+      <c r="L493" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:14:37+00:00</t>
+        </is>
+      </c>
+      <c r="B494" t="n">
+        <v>278.22</v>
+      </c>
+      <c r="C494" t="n">
+        <v>281.05</v>
+      </c>
+      <c r="D494" t="n">
+        <v>283.62</v>
+      </c>
+      <c r="E494" t="n">
+        <v>287.84</v>
+      </c>
+      <c r="F494" t="n">
+        <v>298.69</v>
+      </c>
+      <c r="G494" t="n">
+        <v>318.05</v>
+      </c>
+      <c r="H494" t="n">
+        <v>356.03</v>
+      </c>
+      <c r="I494" t="n">
+        <v>364.61</v>
+      </c>
+      <c r="J494" t="n">
+        <v>332.76</v>
+      </c>
+      <c r="K494" t="n">
+        <v>273.1</v>
+      </c>
+      <c r="L494" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -21046,7 +21172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B560"/>
+  <dimension ref="A1:B563"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26649,6 +26775,36 @@
       </c>
       <c r="B560" t="n">
         <v>-0.18</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B561" t="n">
+        <v>-0.72</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B562" t="n">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B563" t="n">
+        <v>0.48</v>
       </c>
     </row>
   </sheetData>
@@ -26817,28 +26973,28 @@
         <v>0.0578</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3021299133041573</v>
+        <v>-0.3048829769716726</v>
       </c>
       <c r="J2" t="n">
+        <v>493</v>
+      </c>
+      <c r="K2" t="n">
         <v>490</v>
       </c>
-      <c r="K2" t="n">
-        <v>487</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.06113874945344111</v>
+        <v>0.06287117775134454</v>
       </c>
       <c r="M2" t="n">
-        <v>7.336792827227614</v>
+        <v>7.305193913252325</v>
       </c>
       <c r="N2" t="n">
-        <v>81.10081483023315</v>
+        <v>80.64130273834277</v>
       </c>
       <c r="O2" t="n">
-        <v>9.005599082250617</v>
+        <v>8.980050263686879</v>
       </c>
       <c r="P2" t="n">
-        <v>289.3408776431842</v>
+        <v>289.3709282543239</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26895,28 +27051,28 @@
         <v>0.0464</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3405319906344295</v>
+        <v>-0.3357269873790553</v>
       </c>
       <c r="J3" t="n">
+        <v>493</v>
+      </c>
+      <c r="K3" t="n">
         <v>490</v>
       </c>
-      <c r="K3" t="n">
-        <v>487</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.06170678168044763</v>
+        <v>0.06070399247223834</v>
       </c>
       <c r="M3" t="n">
-        <v>8.376859685626584</v>
+        <v>8.350882238586733</v>
       </c>
       <c r="N3" t="n">
-        <v>102.0174390650501</v>
+        <v>101.5082196689588</v>
       </c>
       <c r="O3" t="n">
-        <v>10.10036826383326</v>
+        <v>10.07512876686739</v>
       </c>
       <c r="P3" t="n">
-        <v>287.173115550239</v>
+        <v>287.120691680994</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26973,28 +27129,28 @@
         <v>0.0497</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4552676560184569</v>
+        <v>-0.4499526887578505</v>
       </c>
       <c r="J4" t="n">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="K4" t="n">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09232056337465622</v>
+        <v>0.09127517592692524</v>
       </c>
       <c r="M4" t="n">
-        <v>8.629231514296947</v>
+        <v>8.60523768447972</v>
       </c>
       <c r="N4" t="n">
-        <v>117.9076952767123</v>
+        <v>117.3271030555955</v>
       </c>
       <c r="O4" t="n">
-        <v>10.85853099073315</v>
+        <v>10.83176361704757</v>
       </c>
       <c r="P4" t="n">
-        <v>292.2063237907455</v>
+        <v>292.148416810829</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27051,28 +27207,28 @@
         <v>0.0428</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4314400307485972</v>
+        <v>-0.4320858951906795</v>
       </c>
       <c r="J5" t="n">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="K5" t="n">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09183204585757088</v>
+        <v>0.09309816433434015</v>
       </c>
       <c r="M5" t="n">
-        <v>8.084572444482099</v>
+        <v>8.039573876515282</v>
       </c>
       <c r="N5" t="n">
-        <v>106.5149393387849</v>
+        <v>105.8710710539364</v>
       </c>
       <c r="O5" t="n">
-        <v>10.32060750822281</v>
+        <v>10.28936689276538</v>
       </c>
       <c r="P5" t="n">
-        <v>300.8614032814824</v>
+        <v>300.8684456608996</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27129,28 +27285,28 @@
         <v>0.0483</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2514903986984769</v>
+        <v>-0.2601449586102128</v>
       </c>
       <c r="J6" t="n">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="K6" t="n">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02660846347195001</v>
+        <v>0.02868001178500157</v>
       </c>
       <c r="M6" t="n">
-        <v>9.101862445152857</v>
+        <v>9.091969908979056</v>
       </c>
       <c r="N6" t="n">
-        <v>133.8777246050617</v>
+        <v>133.423335292922</v>
       </c>
       <c r="O6" t="n">
-        <v>11.57055420475016</v>
+        <v>11.55090192551742</v>
       </c>
       <c r="P6" t="n">
-        <v>314.0629523681762</v>
+        <v>314.157203933144</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27207,28 +27363,28 @@
         <v>0.0315</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1100835875231863</v>
+        <v>0.09013568504411555</v>
       </c>
       <c r="J7" t="n">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="K7" t="n">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002640327180930546</v>
+        <v>0.001780489543612429</v>
       </c>
       <c r="M7" t="n">
-        <v>12.69607786282752</v>
+        <v>12.71757785957457</v>
       </c>
       <c r="N7" t="n">
-        <v>262.9601716270441</v>
+        <v>263.2383711397645</v>
       </c>
       <c r="O7" t="n">
-        <v>16.21604673238962</v>
+        <v>16.22462237279391</v>
       </c>
       <c r="P7" t="n">
-        <v>333.8924132159217</v>
+        <v>334.1109348008418</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27285,28 +27441,28 @@
         <v>0.0261</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3548569714634843</v>
+        <v>0.3511591727418644</v>
       </c>
       <c r="J8" t="n">
+        <v>493</v>
+      </c>
+      <c r="K8" t="n">
         <v>490</v>
       </c>
-      <c r="K8" t="n">
-        <v>487</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.01831110583083417</v>
+        <v>0.0181502567300531</v>
       </c>
       <c r="M8" t="n">
-        <v>16.18239001331588</v>
+        <v>16.10325350943338</v>
       </c>
       <c r="N8" t="n">
-        <v>386.3018116469268</v>
+        <v>384.0157968938775</v>
       </c>
       <c r="O8" t="n">
-        <v>19.65456210773791</v>
+        <v>19.59632100405271</v>
       </c>
       <c r="P8" t="n">
-        <v>351.6766359317771</v>
+        <v>351.7172916832709</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27363,28 +27519,28 @@
         <v>0.0209</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5324970595567549</v>
+        <v>0.5366421105595054</v>
       </c>
       <c r="J9" t="n">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="K9" t="n">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03411436990336159</v>
+        <v>0.03503006632206862</v>
       </c>
       <c r="M9" t="n">
-        <v>17.49721434841428</v>
+        <v>17.41245004250742</v>
       </c>
       <c r="N9" t="n">
-        <v>463.5546368652685</v>
+        <v>460.8181941499759</v>
       </c>
       <c r="O9" t="n">
-        <v>21.53031901447975</v>
+        <v>21.46667636477468</v>
       </c>
       <c r="P9" t="n">
-        <v>348.4708673683675</v>
+        <v>348.4256383634488</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27441,28 +27597,28 @@
         <v>0.0283</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6651854098434886</v>
+        <v>0.6703673029832757</v>
       </c>
       <c r="J10" t="n">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="K10" t="n">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="L10" t="n">
-        <v>0.03894578246191915</v>
+        <v>0.03998631902196847</v>
       </c>
       <c r="M10" t="n">
-        <v>19.79052351062181</v>
+        <v>19.69187658839059</v>
       </c>
       <c r="N10" t="n">
-        <v>627.1641373167862</v>
+        <v>623.4929647924555</v>
       </c>
       <c r="O10" t="n">
-        <v>25.04324534314166</v>
+        <v>24.96984110466976</v>
       </c>
       <c r="P10" t="n">
-        <v>313.0688743588055</v>
+        <v>313.0121893056368</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -27519,28 +27675,28 @@
         <v>0.0801</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4587516269971845</v>
+        <v>0.4321610604092345</v>
       </c>
       <c r="J11" t="n">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="K11" t="n">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01252985115935468</v>
+        <v>0.01123020359893656</v>
       </c>
       <c r="M11" t="n">
-        <v>24.90656330096177</v>
+        <v>24.90618348682996</v>
       </c>
       <c r="N11" t="n">
-        <v>957.2360856620827</v>
+        <v>954.740357129155</v>
       </c>
       <c r="O11" t="n">
-        <v>30.93923214402844</v>
+        <v>30.89887307215515</v>
       </c>
       <c r="P11" t="n">
-        <v>286.5392405280729</v>
+        <v>286.8299110327997</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -27582,7 +27738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L491"/>
+  <dimension ref="A1:L494"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57951,6 +58107,192 @@
         </is>
       </c>
     </row>
+    <row r="492">
+      <c r="A492" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:14:25+00:00</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>-45.90691869465279,170.56359012470523</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>-45.90707990809511,170.56271941120855</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>-45.90722448224592,170.56184435045907</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>-45.90738392514343,170.56097317326447</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>-45.90760502875512,170.56013667601783</t>
+        </is>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>-45.907858586568544,170.559302745278</t>
+        </is>
+      </c>
+      <c r="H492" t="inlineStr">
+        <is>
+          <t>-45.90824446729853,170.5584296523641</t>
+        </is>
+      </c>
+      <c r="I492" t="inlineStr">
+        <is>
+          <t>-45.908351355612034,170.55752975563203</t>
+        </is>
+      </c>
+      <c r="J492" t="inlineStr">
+        <is>
+          <t>-45.90808283034977,170.5566336185025</t>
+        </is>
+      </c>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>-45.90739308640011,170.55598196166238</t>
+        </is>
+      </c>
+      <c r="L492" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:37+00:00</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>-45.90691577396813,170.56358936169528</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>-45.90707309315719,170.56271763092076</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>-45.90721890638183,170.56184289391697</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>-45.90737746421489,170.5609714855904</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>-45.90759505627881,170.56013461118104</t>
+        </is>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>-45.90784781554354,170.55930169752938</t>
+        </is>
+      </c>
+      <c r="H493" t="inlineStr">
+        <is>
+          <t>-45.908229359534594,170.55842902271309</t>
+        </is>
+      </c>
+      <c r="I493" t="inlineStr">
+        <is>
+          <t>-45.90833858172867,170.55752950761388</t>
+        </is>
+      </c>
+      <c r="J493" t="inlineStr">
+        <is>
+          <t>-45.90808051363841,170.5566340809355</t>
+        </is>
+      </c>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>-45.90740486435057,170.55597721466765</t>
+        </is>
+      </c>
+      <c r="L493" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:14:37+00:00</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>-45.90691064064354,170.56358802064767</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>-45.90706052534952,170.56271434779373</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>-45.90720810867671,170.56184007331234</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>-45.90737029523935,170.56096961296618</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>-45.90758873444111,170.56013330222234</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>-45.907838211379556,170.5593007632871</t>
+        </is>
+      </c>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>-45.908210294975305,170.55842822815364</t>
+        </is>
+      </c>
+      <c r="I494" t="inlineStr">
+        <is>
+          <t>-45.90831861129128,170.55752911986716</t>
+        </is>
+      </c>
+      <c r="J494" t="inlineStr">
+        <is>
+          <t>-45.90804300073472,170.55664156878672</t>
+        </is>
+      </c>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>-45.90737005011396,170.5559912462195</t>
+        </is>
+      </c>
+      <c r="L494" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
